--- a/trades/suggested_trades_by_strategy.xlsx
+++ b/trades/suggested_trades_by_strategy.xlsx
@@ -689,7 +689,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Generated on 2026-10-29 01:58:45 IST | All Active Strategies Analyzed</t>
+          <t>Generated on 2026-10-29 02:07:44 IST | All Active Strategies Analyzed</t>
         </is>
       </c>
     </row>
@@ -775,10 +775,10 @@
         <v>2130.7</v>
       </c>
       <c r="J6" s="8" t="n">
-        <v>145674</v>
+        <v>143369</v>
       </c>
       <c r="K6" s="7" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1">
@@ -811,10 +811,10 @@
         <v>1046.5</v>
       </c>
       <c r="J7" s="13" t="n">
-        <v>75628</v>
+        <v>75161</v>
       </c>
       <c r="K7" s="12" t="n">
-        <v>3.43</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1">
@@ -847,10 +847,10 @@
         <v>888.5</v>
       </c>
       <c r="J8" s="18" t="n">
-        <v>55674</v>
+        <v>53501</v>
       </c>
       <c r="K8" s="17" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1">
@@ -883,10 +883,10 @@
         <v>195.7</v>
       </c>
       <c r="J9" s="13" t="n">
-        <v>14372</v>
+        <v>14707</v>
       </c>
       <c r="K9" s="12" t="n">
-        <v>5.04</v>
+        <v>5.57</v>
       </c>
     </row>
     <row r="12">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="D2" s="23" t="inlineStr">
         <is>
-          <t>Trendline Breakout [Tier 3 (Expensive]</t>
+          <t>Trendline Breakout [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E2" s="22" t="inlineStr">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="P2" s="23" t="inlineStr">
         <is>
-          <t>NIFTY 22600 CE</t>
+          <t>NIFTY 22700 CE</t>
         </is>
       </c>
       <c r="Q2" s="22" t="inlineStr">
@@ -1181,22 +1181,22 @@
         </is>
       </c>
       <c r="R2" s="24" t="n">
-        <v>197.51</v>
+        <v>151.21</v>
       </c>
       <c r="S2" s="24" t="n">
-        <v>237.89</v>
+        <v>185.32</v>
       </c>
       <c r="T2" s="26" t="n">
-        <v>25676</v>
+        <v>19657</v>
       </c>
       <c r="U2" s="26" t="n">
-        <v>30926</v>
+        <v>24092</v>
       </c>
       <c r="V2" s="27" t="n">
-        <v>5147</v>
+        <v>4344</v>
       </c>
       <c r="W2" s="28" t="n">
-        <v>20</v>
+        <v>22.1</v>
       </c>
       <c r="X2" s="22" t="n">
         <v>2</v>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="D6" s="23" t="inlineStr">
         <is>
-          <t>OR-30H Support Flip [Tier 3 (Expensive]</t>
+          <t>OR-30H Support Flip [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E6" s="22" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="P6" s="23" t="inlineStr">
         <is>
-          <t>NIFTY 22700 CE</t>
+          <t>NIFTY 22800 CE</t>
         </is>
       </c>
       <c r="Q6" s="22" t="inlineStr">
@@ -1589,22 +1589,22 @@
         </is>
       </c>
       <c r="R6" s="24" t="n">
-        <v>175.94</v>
+        <v>129.77</v>
       </c>
       <c r="S6" s="24" t="n">
-        <v>195.3</v>
+        <v>145.68</v>
       </c>
       <c r="T6" s="26" t="n">
-        <v>22872</v>
+        <v>16870</v>
       </c>
       <c r="U6" s="26" t="n">
-        <v>25389</v>
+        <v>18938</v>
       </c>
       <c r="V6" s="27" t="n">
-        <v>2424</v>
+        <v>1987</v>
       </c>
       <c r="W6" s="28" t="n">
-        <v>10.6</v>
+        <v>11.8</v>
       </c>
       <c r="X6" s="22" t="n">
         <v>2</v>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="D7" s="30" t="inlineStr">
         <is>
-          <t>PDL Resistance Flip [Tier 3 (Expensive]</t>
+          <t>PDL Resistance Flip [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E7" s="29" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="P7" s="30" t="inlineStr">
         <is>
-          <t>NIFTY 22800 PE</t>
+          <t>NIFTY 22700 PE</t>
         </is>
       </c>
       <c r="Q7" s="29" t="inlineStr">
@@ -1691,22 +1691,22 @@
         </is>
       </c>
       <c r="R7" s="31" t="n">
-        <v>165.38</v>
+        <v>121.21</v>
       </c>
       <c r="S7" s="31" t="n">
-        <v>215.48</v>
+        <v>162.55</v>
       </c>
       <c r="T7" s="33" t="n">
-        <v>21499</v>
+        <v>15757</v>
       </c>
       <c r="U7" s="33" t="n">
-        <v>28012</v>
+        <v>21132</v>
       </c>
       <c r="V7" s="34" t="n">
-        <v>6417</v>
+        <v>5290</v>
       </c>
       <c r="W7" s="35" t="n">
-        <v>29.8</v>
+        <v>33.6</v>
       </c>
       <c r="X7" s="29" t="n">
         <v>2</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="D8" s="23" t="inlineStr">
         <is>
-          <t>OR-30L Resistance Flip [Tier 3 (Expensive]</t>
+          <t>OR-30L Resistance Flip [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="P8" s="23" t="inlineStr">
         <is>
-          <t>NIFTY 22950 PE</t>
+          <t>NIFTY 22850 PE</t>
         </is>
       </c>
       <c r="Q8" s="22" t="inlineStr">
@@ -1793,22 +1793,22 @@
         </is>
       </c>
       <c r="R8" s="24" t="n">
-        <v>183.47</v>
+        <v>136.34</v>
       </c>
       <c r="S8" s="24" t="n">
-        <v>162.23</v>
+        <v>118.95</v>
       </c>
       <c r="T8" s="26" t="n">
-        <v>23851</v>
+        <v>17724</v>
       </c>
       <c r="U8" s="26" t="n">
-        <v>21090</v>
+        <v>15464</v>
       </c>
       <c r="V8" s="37" t="n">
-        <v>-2849</v>
+        <v>-2338</v>
       </c>
       <c r="W8" s="38" t="n">
-        <v>-11.9</v>
+        <v>-13.2</v>
       </c>
       <c r="X8" s="22" t="n">
         <v>2</v>
@@ -3722,7 +3722,7 @@
       </c>
       <c r="P27" s="30" t="inlineStr">
         <is>
-          <t>NIFTY 22600 PE</t>
+          <t>NIFTY 22550 PE</t>
         </is>
       </c>
       <c r="Q27" s="29" t="inlineStr">
@@ -3731,22 +3731,22 @@
         </is>
       </c>
       <c r="R27" s="31" t="n">
-        <v>170.5</v>
+        <v>145.36</v>
       </c>
       <c r="S27" s="31" t="n">
-        <v>152.11</v>
+        <v>128.78</v>
       </c>
       <c r="T27" s="33" t="n">
-        <v>22165</v>
+        <v>18897</v>
       </c>
       <c r="U27" s="33" t="n">
-        <v>19774</v>
+        <v>16741</v>
       </c>
       <c r="V27" s="40" t="n">
-        <v>-2476</v>
+        <v>-2235</v>
       </c>
       <c r="W27" s="41" t="n">
-        <v>-11.2</v>
+        <v>-11.8</v>
       </c>
       <c r="X27" s="29" t="n">
         <v>2</v>
@@ -3880,7 +3880,7 @@
       </c>
       <c r="D29" s="30" t="inlineStr">
         <is>
-          <t>Trendline Breakout [Tier 3 (Expensive]</t>
+          <t>Trendline Breakout [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E29" s="29" t="inlineStr">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="P29" s="30" t="inlineStr">
         <is>
-          <t>NIFTY 22700 CE</t>
+          <t>NIFTY 22800 CE</t>
         </is>
       </c>
       <c r="Q29" s="29" t="inlineStr">
@@ -3935,22 +3935,22 @@
         </is>
       </c>
       <c r="R29" s="31" t="n">
-        <v>166.67</v>
+        <v>120.65</v>
       </c>
       <c r="S29" s="31" t="n">
-        <v>147.4</v>
+        <v>105.17</v>
       </c>
       <c r="T29" s="33" t="n">
-        <v>21667</v>
+        <v>15684</v>
       </c>
       <c r="U29" s="33" t="n">
-        <v>19162</v>
+        <v>13672</v>
       </c>
       <c r="V29" s="40" t="n">
-        <v>-2589</v>
+        <v>-2086</v>
       </c>
       <c r="W29" s="41" t="n">
-        <v>-11.9</v>
+        <v>-13.3</v>
       </c>
       <c r="X29" s="29" t="n">
         <v>2</v>
@@ -6532,7 +6532,7 @@
       </c>
       <c r="D55" s="30" t="inlineStr">
         <is>
-          <t>Trendline Breakdown [Tier 3 (Expensive]</t>
+          <t>Trendline Breakdown [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E55" s="29" t="inlineStr">
@@ -6578,7 +6578,7 @@
       </c>
       <c r="P55" s="30" t="inlineStr">
         <is>
-          <t>NIFTY 23250 PE</t>
+          <t>NIFTY 23150 PE</t>
         </is>
       </c>
       <c r="Q55" s="29" t="inlineStr">
@@ -6587,22 +6587,22 @@
         </is>
       </c>
       <c r="R55" s="31" t="n">
-        <v>163.36</v>
+        <v>117.45</v>
       </c>
       <c r="S55" s="31" t="n">
-        <v>170.08</v>
+        <v>122.71</v>
       </c>
       <c r="T55" s="33" t="n">
-        <v>21237</v>
+        <v>15268</v>
       </c>
       <c r="U55" s="33" t="n">
-        <v>22110</v>
+        <v>15952</v>
       </c>
       <c r="V55" s="34" t="n">
-        <v>786</v>
+        <v>607</v>
       </c>
       <c r="W55" s="35" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="X55" s="29" t="n">
         <v>2</v>
@@ -11020,7 +11020,7 @@
       </c>
       <c r="D99" s="30" t="inlineStr">
         <is>
-          <t>OR-30L Resistance Flip [Tier 3 (Expensive]</t>
+          <t>OR-30L Resistance Flip [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E99" s="29" t="inlineStr">
@@ -11066,7 +11066,7 @@
       </c>
       <c r="P99" s="30" t="inlineStr">
         <is>
-          <t>NIFTY 24400 PE</t>
+          <t>NIFTY 24300 PE</t>
         </is>
       </c>
       <c r="Q99" s="29" t="inlineStr">
@@ -11075,22 +11075,22 @@
         </is>
       </c>
       <c r="R99" s="31" t="n">
-        <v>162.85</v>
+        <v>115.25</v>
       </c>
       <c r="S99" s="31" t="n">
-        <v>214.25</v>
+        <v>157.06</v>
       </c>
       <c r="T99" s="33" t="n">
-        <v>21170</v>
+        <v>14982</v>
       </c>
       <c r="U99" s="33" t="n">
-        <v>27852</v>
+        <v>20418</v>
       </c>
       <c r="V99" s="34" t="n">
-        <v>6586</v>
+        <v>5353</v>
       </c>
       <c r="W99" s="35" t="n">
-        <v>31.1</v>
+        <v>35.7</v>
       </c>
       <c r="X99" s="29" t="n">
         <v>2</v>
@@ -11122,7 +11122,7 @@
       </c>
       <c r="D100" s="23" t="inlineStr">
         <is>
-          <t>PDL Resistance Flip [Tier 3 (Expensive]</t>
+          <t>PDL Resistance Flip [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E100" s="22" t="inlineStr">
@@ -11168,7 +11168,7 @@
       </c>
       <c r="P100" s="23" t="inlineStr">
         <is>
-          <t>NIFTY 24450 PE</t>
+          <t>NIFTY 24350 PE</t>
         </is>
       </c>
       <c r="Q100" s="22" t="inlineStr">
@@ -11177,22 +11177,22 @@
         </is>
       </c>
       <c r="R100" s="24" t="n">
-        <v>162.38</v>
+        <v>115.03</v>
       </c>
       <c r="S100" s="24" t="n">
-        <v>192.28</v>
+        <v>139.14</v>
       </c>
       <c r="T100" s="26" t="n">
-        <v>21109</v>
+        <v>14954</v>
       </c>
       <c r="U100" s="26" t="n">
-        <v>24996</v>
+        <v>18088</v>
       </c>
       <c r="V100" s="27" t="n">
-        <v>3795</v>
+        <v>3055</v>
       </c>
       <c r="W100" s="28" t="n">
-        <v>18</v>
+        <v>20.4</v>
       </c>
       <c r="X100" s="22" t="n">
         <v>2</v>
@@ -11836,7 +11836,7 @@
       </c>
       <c r="D107" s="30" t="inlineStr">
         <is>
-          <t>Trendline Breakout [Tier 3 (Expensive]</t>
+          <t>Trendline Breakout [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E107" s="29" t="inlineStr">
@@ -11882,7 +11882,7 @@
       </c>
       <c r="P107" s="30" t="inlineStr">
         <is>
-          <t>NIFTY 24600 CE</t>
+          <t>NIFTY 24700 CE</t>
         </is>
       </c>
       <c r="Q107" s="29" t="inlineStr">
@@ -11891,22 +11891,22 @@
         </is>
       </c>
       <c r="R107" s="31" t="n">
-        <v>160.62</v>
+        <v>115.06</v>
       </c>
       <c r="S107" s="31" t="n">
-        <v>160.27</v>
+        <v>114.72</v>
       </c>
       <c r="T107" s="33" t="n">
-        <v>20881</v>
+        <v>14958</v>
       </c>
       <c r="U107" s="33" t="n">
-        <v>20835</v>
+        <v>14914</v>
       </c>
       <c r="V107" s="40" t="n">
-        <v>-131</v>
+        <v>-119</v>
       </c>
       <c r="W107" s="41" t="n">
-        <v>-0.6</v>
+        <v>-0.8</v>
       </c>
       <c r="X107" s="29" t="n">
         <v>2</v>
@@ -11938,7 +11938,7 @@
       </c>
       <c r="D108" s="23" t="inlineStr">
         <is>
-          <t>OR-30L Resistance Flip [Tier 3 (Expensive]</t>
+          <t>OR-30L Resistance Flip [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E108" s="22" t="inlineStr">
@@ -11984,7 +11984,7 @@
       </c>
       <c r="P108" s="23" t="inlineStr">
         <is>
-          <t>NIFTY 24600 PE</t>
+          <t>NIFTY 24500 PE</t>
         </is>
       </c>
       <c r="Q108" s="22" t="inlineStr">
@@ -11993,22 +11993,22 @@
         </is>
       </c>
       <c r="R108" s="24" t="n">
-        <v>164.92</v>
+        <v>117.91</v>
       </c>
       <c r="S108" s="24" t="n">
-        <v>142.15</v>
+        <v>99.77</v>
       </c>
       <c r="T108" s="26" t="n">
-        <v>21440</v>
+        <v>15328</v>
       </c>
       <c r="U108" s="26" t="n">
-        <v>18480</v>
+        <v>12970</v>
       </c>
       <c r="V108" s="37" t="n">
-        <v>-3043</v>
+        <v>-2431</v>
       </c>
       <c r="W108" s="38" t="n">
-        <v>-14.2</v>
+        <v>-15.9</v>
       </c>
       <c r="X108" s="22" t="n">
         <v>2</v>
@@ -12086,7 +12086,7 @@
       </c>
       <c r="P109" s="30" t="inlineStr">
         <is>
-          <t>NIFTY 24600 PE</t>
+          <t>NIFTY 24550 PE</t>
         </is>
       </c>
       <c r="Q109" s="29" t="inlineStr">
@@ -12095,22 +12095,22 @@
         </is>
       </c>
       <c r="R109" s="31" t="n">
-        <v>160.74</v>
+        <v>136.4</v>
       </c>
       <c r="S109" s="31" t="n">
-        <v>136.27</v>
+        <v>114.46</v>
       </c>
       <c r="T109" s="33" t="n">
-        <v>20896</v>
+        <v>17732</v>
       </c>
       <c r="U109" s="33" t="n">
-        <v>17715</v>
+        <v>14880</v>
       </c>
       <c r="V109" s="40" t="n">
-        <v>-3263</v>
+        <v>-2928</v>
       </c>
       <c r="W109" s="41" t="n">
-        <v>-15.6</v>
+        <v>-16.5</v>
       </c>
       <c r="X109" s="29" t="n">
         <v>2</v>
@@ -12521,7 +12521,7 @@
       </c>
       <c r="D2" s="23" t="inlineStr">
         <is>
-          <t>Trendline Breakout [Tier 3 (Expensive]</t>
+          <t>Trendline Breakout [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E2" s="22" t="inlineStr">
@@ -12567,7 +12567,7 @@
       </c>
       <c r="P2" s="23" t="inlineStr">
         <is>
-          <t>NIFTY 22600 CE</t>
+          <t>NIFTY 22700 CE</t>
         </is>
       </c>
       <c r="Q2" s="22" t="inlineStr">
@@ -12576,22 +12576,22 @@
         </is>
       </c>
       <c r="R2" s="24" t="n">
-        <v>197.51</v>
+        <v>151.21</v>
       </c>
       <c r="S2" s="24" t="n">
-        <v>237.89</v>
+        <v>185.32</v>
       </c>
       <c r="T2" s="26" t="n">
-        <v>25676</v>
+        <v>19657</v>
       </c>
       <c r="U2" s="26" t="n">
-        <v>30926</v>
+        <v>24092</v>
       </c>
       <c r="V2" s="27" t="n">
-        <v>5147</v>
+        <v>4344</v>
       </c>
       <c r="W2" s="28" t="n">
-        <v>20</v>
+        <v>22.1</v>
       </c>
       <c r="X2" s="22" t="n">
         <v>2</v>
@@ -13847,7 +13847,7 @@
       </c>
       <c r="D15" s="30" t="inlineStr">
         <is>
-          <t>Trendline Breakout [Tier 3 (Expensive]</t>
+          <t>Trendline Breakout [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E15" s="29" t="inlineStr">
@@ -13893,7 +13893,7 @@
       </c>
       <c r="P15" s="30" t="inlineStr">
         <is>
-          <t>NIFTY 22700 CE</t>
+          <t>NIFTY 22800 CE</t>
         </is>
       </c>
       <c r="Q15" s="29" t="inlineStr">
@@ -13902,22 +13902,22 @@
         </is>
       </c>
       <c r="R15" s="31" t="n">
-        <v>166.67</v>
+        <v>120.65</v>
       </c>
       <c r="S15" s="31" t="n">
-        <v>147.4</v>
+        <v>105.17</v>
       </c>
       <c r="T15" s="33" t="n">
-        <v>21667</v>
+        <v>15684</v>
       </c>
       <c r="U15" s="33" t="n">
-        <v>19162</v>
+        <v>13672</v>
       </c>
       <c r="V15" s="40" t="n">
-        <v>-2589</v>
+        <v>-2086</v>
       </c>
       <c r="W15" s="41" t="n">
-        <v>-11.9</v>
+        <v>-13.3</v>
       </c>
       <c r="X15" s="29" t="n">
         <v>2</v>
@@ -15683,7 +15683,7 @@
       </c>
       <c r="D33" s="30" t="inlineStr">
         <is>
-          <t>Trendline Breakdown [Tier 3 (Expensive]</t>
+          <t>Trendline Breakdown [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E33" s="29" t="inlineStr">
@@ -15729,7 +15729,7 @@
       </c>
       <c r="P33" s="30" t="inlineStr">
         <is>
-          <t>NIFTY 23250 PE</t>
+          <t>NIFTY 23150 PE</t>
         </is>
       </c>
       <c r="Q33" s="29" t="inlineStr">
@@ -15738,22 +15738,22 @@
         </is>
       </c>
       <c r="R33" s="31" t="n">
-        <v>163.36</v>
+        <v>117.45</v>
       </c>
       <c r="S33" s="31" t="n">
-        <v>170.08</v>
+        <v>122.71</v>
       </c>
       <c r="T33" s="33" t="n">
-        <v>21237</v>
+        <v>15268</v>
       </c>
       <c r="U33" s="33" t="n">
-        <v>22110</v>
+        <v>15952</v>
       </c>
       <c r="V33" s="34" t="n">
-        <v>786</v>
+        <v>607</v>
       </c>
       <c r="W33" s="35" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="X33" s="29" t="n">
         <v>2</v>
@@ -17417,7 +17417,7 @@
       </c>
       <c r="D50" s="23" t="inlineStr">
         <is>
-          <t>Trendline Breakout [Tier 3 (Expensive]</t>
+          <t>Trendline Breakout [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E50" s="22" t="inlineStr">
@@ -17463,7 +17463,7 @@
       </c>
       <c r="P50" s="23" t="inlineStr">
         <is>
-          <t>NIFTY 24600 CE</t>
+          <t>NIFTY 24700 CE</t>
         </is>
       </c>
       <c r="Q50" s="22" t="inlineStr">
@@ -17472,22 +17472,22 @@
         </is>
       </c>
       <c r="R50" s="24" t="n">
-        <v>160.62</v>
+        <v>115.06</v>
       </c>
       <c r="S50" s="24" t="n">
-        <v>160.27</v>
+        <v>114.72</v>
       </c>
       <c r="T50" s="26" t="n">
-        <v>20881</v>
+        <v>14958</v>
       </c>
       <c r="U50" s="26" t="n">
-        <v>20835</v>
+        <v>14914</v>
       </c>
       <c r="V50" s="37" t="n">
-        <v>-131</v>
+        <v>-119</v>
       </c>
       <c r="W50" s="38" t="n">
-        <v>-0.6</v>
+        <v>-0.8</v>
       </c>
       <c r="X50" s="22" t="n">
         <v>2</v>
@@ -17694,7 +17694,7 @@
       </c>
       <c r="D2" s="23" t="inlineStr">
         <is>
-          <t>OR-30H Support Flip [Tier 3 (Expensive]</t>
+          <t>OR-30H Support Flip [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E2" s="22" t="inlineStr">
@@ -17740,7 +17740,7 @@
       </c>
       <c r="P2" s="23" t="inlineStr">
         <is>
-          <t>NIFTY 22700 CE</t>
+          <t>NIFTY 22800 CE</t>
         </is>
       </c>
       <c r="Q2" s="22" t="inlineStr">
@@ -17749,22 +17749,22 @@
         </is>
       </c>
       <c r="R2" s="24" t="n">
-        <v>175.94</v>
+        <v>129.77</v>
       </c>
       <c r="S2" s="24" t="n">
-        <v>195.3</v>
+        <v>145.68</v>
       </c>
       <c r="T2" s="26" t="n">
-        <v>22872</v>
+        <v>16870</v>
       </c>
       <c r="U2" s="26" t="n">
-        <v>25389</v>
+        <v>18938</v>
       </c>
       <c r="V2" s="27" t="n">
-        <v>2424</v>
+        <v>1987</v>
       </c>
       <c r="W2" s="28" t="n">
-        <v>10.6</v>
+        <v>11.8</v>
       </c>
       <c r="X2" s="22" t="n">
         <v>2</v>
@@ -17796,7 +17796,7 @@
       </c>
       <c r="D3" s="30" t="inlineStr">
         <is>
-          <t>PDL Resistance Flip [Tier 3 (Expensive]</t>
+          <t>PDL Resistance Flip [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E3" s="29" t="inlineStr">
@@ -17842,7 +17842,7 @@
       </c>
       <c r="P3" s="30" t="inlineStr">
         <is>
-          <t>NIFTY 22800 PE</t>
+          <t>NIFTY 22700 PE</t>
         </is>
       </c>
       <c r="Q3" s="29" t="inlineStr">
@@ -17851,22 +17851,22 @@
         </is>
       </c>
       <c r="R3" s="31" t="n">
-        <v>165.38</v>
+        <v>121.21</v>
       </c>
       <c r="S3" s="31" t="n">
-        <v>215.48</v>
+        <v>162.55</v>
       </c>
       <c r="T3" s="33" t="n">
-        <v>21499</v>
+        <v>15757</v>
       </c>
       <c r="U3" s="33" t="n">
-        <v>28012</v>
+        <v>21132</v>
       </c>
       <c r="V3" s="34" t="n">
-        <v>6417</v>
+        <v>5290</v>
       </c>
       <c r="W3" s="35" t="n">
-        <v>29.8</v>
+        <v>33.6</v>
       </c>
       <c r="X3" s="29" t="n">
         <v>2</v>
@@ -17898,7 +17898,7 @@
       </c>
       <c r="D4" s="23" t="inlineStr">
         <is>
-          <t>OR-30L Resistance Flip [Tier 3 (Expensive]</t>
+          <t>OR-30L Resistance Flip [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E4" s="22" t="inlineStr">
@@ -17944,7 +17944,7 @@
       </c>
       <c r="P4" s="23" t="inlineStr">
         <is>
-          <t>NIFTY 22950 PE</t>
+          <t>NIFTY 22850 PE</t>
         </is>
       </c>
       <c r="Q4" s="22" t="inlineStr">
@@ -17953,22 +17953,22 @@
         </is>
       </c>
       <c r="R4" s="24" t="n">
-        <v>183.47</v>
+        <v>136.34</v>
       </c>
       <c r="S4" s="24" t="n">
-        <v>162.23</v>
+        <v>118.95</v>
       </c>
       <c r="T4" s="26" t="n">
-        <v>23851</v>
+        <v>17724</v>
       </c>
       <c r="U4" s="26" t="n">
-        <v>21090</v>
+        <v>15464</v>
       </c>
       <c r="V4" s="37" t="n">
-        <v>-2849</v>
+        <v>-2338</v>
       </c>
       <c r="W4" s="38" t="n">
-        <v>-11.9</v>
+        <v>-13.2</v>
       </c>
       <c r="X4" s="22" t="n">
         <v>2</v>
@@ -19066,7 +19066,7 @@
       </c>
       <c r="P15" s="30" t="inlineStr">
         <is>
-          <t>NIFTY 22600 PE</t>
+          <t>NIFTY 22550 PE</t>
         </is>
       </c>
       <c r="Q15" s="29" t="inlineStr">
@@ -19075,22 +19075,22 @@
         </is>
       </c>
       <c r="R15" s="31" t="n">
-        <v>170.5</v>
+        <v>145.36</v>
       </c>
       <c r="S15" s="31" t="n">
-        <v>152.11</v>
+        <v>128.78</v>
       </c>
       <c r="T15" s="33" t="n">
-        <v>22165</v>
+        <v>18897</v>
       </c>
       <c r="U15" s="33" t="n">
-        <v>19774</v>
+        <v>16741</v>
       </c>
       <c r="V15" s="40" t="n">
-        <v>-2476</v>
+        <v>-2235</v>
       </c>
       <c r="W15" s="41" t="n">
-        <v>-11.2</v>
+        <v>-11.8</v>
       </c>
       <c r="X15" s="29" t="n">
         <v>2</v>
@@ -22488,7 +22488,7 @@
       </c>
       <c r="D49" s="30" t="inlineStr">
         <is>
-          <t>OR-30L Resistance Flip [Tier 3 (Expensive]</t>
+          <t>OR-30L Resistance Flip [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E49" s="29" t="inlineStr">
@@ -22534,7 +22534,7 @@
       </c>
       <c r="P49" s="30" t="inlineStr">
         <is>
-          <t>NIFTY 24400 PE</t>
+          <t>NIFTY 24300 PE</t>
         </is>
       </c>
       <c r="Q49" s="29" t="inlineStr">
@@ -22543,22 +22543,22 @@
         </is>
       </c>
       <c r="R49" s="31" t="n">
-        <v>162.85</v>
+        <v>115.25</v>
       </c>
       <c r="S49" s="31" t="n">
-        <v>214.25</v>
+        <v>157.06</v>
       </c>
       <c r="T49" s="33" t="n">
-        <v>21170</v>
+        <v>14982</v>
       </c>
       <c r="U49" s="33" t="n">
-        <v>27852</v>
+        <v>20418</v>
       </c>
       <c r="V49" s="34" t="n">
-        <v>6586</v>
+        <v>5353</v>
       </c>
       <c r="W49" s="35" t="n">
-        <v>31.1</v>
+        <v>35.7</v>
       </c>
       <c r="X49" s="29" t="n">
         <v>2</v>
@@ -22590,7 +22590,7 @@
       </c>
       <c r="D50" s="23" t="inlineStr">
         <is>
-          <t>PDL Resistance Flip [Tier 3 (Expensive]</t>
+          <t>PDL Resistance Flip [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E50" s="22" t="inlineStr">
@@ -22636,7 +22636,7 @@
       </c>
       <c r="P50" s="23" t="inlineStr">
         <is>
-          <t>NIFTY 24450 PE</t>
+          <t>NIFTY 24350 PE</t>
         </is>
       </c>
       <c r="Q50" s="22" t="inlineStr">
@@ -22645,22 +22645,22 @@
         </is>
       </c>
       <c r="R50" s="24" t="n">
-        <v>162.38</v>
+        <v>115.03</v>
       </c>
       <c r="S50" s="24" t="n">
-        <v>192.28</v>
+        <v>139.14</v>
       </c>
       <c r="T50" s="26" t="n">
-        <v>21109</v>
+        <v>14954</v>
       </c>
       <c r="U50" s="26" t="n">
-        <v>24996</v>
+        <v>18088</v>
       </c>
       <c r="V50" s="27" t="n">
-        <v>3795</v>
+        <v>3055</v>
       </c>
       <c r="W50" s="28" t="n">
-        <v>18</v>
+        <v>20.4</v>
       </c>
       <c r="X50" s="22" t="n">
         <v>2</v>
@@ -22896,7 +22896,7 @@
       </c>
       <c r="D53" s="30" t="inlineStr">
         <is>
-          <t>OR-30L Resistance Flip [Tier 3 (Expensive]</t>
+          <t>OR-30L Resistance Flip [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E53" s="29" t="inlineStr">
@@ -22942,7 +22942,7 @@
       </c>
       <c r="P53" s="30" t="inlineStr">
         <is>
-          <t>NIFTY 24600 PE</t>
+          <t>NIFTY 24500 PE</t>
         </is>
       </c>
       <c r="Q53" s="29" t="inlineStr">
@@ -22951,22 +22951,22 @@
         </is>
       </c>
       <c r="R53" s="31" t="n">
-        <v>164.92</v>
+        <v>117.91</v>
       </c>
       <c r="S53" s="31" t="n">
-        <v>142.15</v>
+        <v>99.77</v>
       </c>
       <c r="T53" s="33" t="n">
-        <v>21440</v>
+        <v>15328</v>
       </c>
       <c r="U53" s="33" t="n">
-        <v>18480</v>
+        <v>12970</v>
       </c>
       <c r="V53" s="40" t="n">
-        <v>-3043</v>
+        <v>-2431</v>
       </c>
       <c r="W53" s="41" t="n">
-        <v>-14.2</v>
+        <v>-15.9</v>
       </c>
       <c r="X53" s="29" t="n">
         <v>2</v>
@@ -24035,7 +24035,7 @@
       </c>
       <c r="P8" s="23" t="inlineStr">
         <is>
-          <t>NIFTY 24600 PE</t>
+          <t>NIFTY 24550 PE</t>
         </is>
       </c>
       <c r="Q8" s="22" t="inlineStr">
@@ -24044,22 +24044,22 @@
         </is>
       </c>
       <c r="R8" s="24" t="n">
-        <v>160.74</v>
+        <v>136.4</v>
       </c>
       <c r="S8" s="24" t="n">
-        <v>136.27</v>
+        <v>114.46</v>
       </c>
       <c r="T8" s="26" t="n">
-        <v>20896</v>
+        <v>17732</v>
       </c>
       <c r="U8" s="26" t="n">
-        <v>17715</v>
+        <v>14880</v>
       </c>
       <c r="V8" s="37" t="n">
-        <v>-3263</v>
+        <v>-2928</v>
       </c>
       <c r="W8" s="38" t="n">
-        <v>-15.6</v>
+        <v>-16.5</v>
       </c>
       <c r="X8" s="22" t="n">
         <v>2</v>
